--- a/orcamentos_gerados/Orcamento_Lucas_Zillmer.xlsx
+++ b/orcamentos_gerados/Orcamento_Lucas_Zillmer.xlsx
@@ -4085,7 +4085,9 @@
           <t>CARRETA 1</t>
         </is>
       </c>
-      <c r="K7" s="314" t="n"/>
+      <c r="K7" s="314" t="n">
+        <v>600</v>
+      </c>
       <c r="L7" s="20" t="n"/>
       <c r="M7" s="18" t="n"/>
       <c r="N7" s="3" t="n"/>
@@ -4238,7 +4240,9 @@
           <t>CARRETA 2</t>
         </is>
       </c>
-      <c r="K8" s="315" t="n"/>
+      <c r="K8" s="315" t="n">
+        <v>950</v>
+      </c>
       <c r="L8" s="20" t="n"/>
       <c r="M8" s="21" t="inlineStr">
         <is>
@@ -6693,7 +6697,11 @@
       </c>
       <c r="F23" s="332" t="n"/>
       <c r="G23" s="333" t="n"/>
-      <c r="H23" s="353" t="n"/>
+      <c r="H23" s="353" t="inlineStr">
+        <is>
+          <t>10 dias</t>
+        </is>
+      </c>
       <c r="I23" s="325" t="n"/>
       <c r="K23" s="195" t="n"/>
       <c r="L23" s="303" t="n"/>
